--- a/cobros.xlsx
+++ b/cobros.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,21 +508,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12AF16C1E2</t>
+          <t>AE36BA020C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,11 +533,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -545,17 +549,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -577,21 +581,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D955C0CC5B</t>
+          <t>5C64AC5BBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -600,11 +606,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -614,17 +622,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -646,21 +654,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0A6DB09538</t>
+          <t>9E03386940</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -669,11 +679,13 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -683,17 +695,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -715,21 +727,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>78A848DF17</t>
+          <t>C92E8B110F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -738,11 +752,13 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -752,17 +768,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -784,21 +800,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8EB139C859</t>
+          <t>A592DD4539</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -807,11 +825,13 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -826,12 +846,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -853,21 +873,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>213B916B55</t>
+          <t>1C98984DFE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -876,11 +898,13 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -890,17 +914,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -922,21 +946,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1F1D15A9E5</t>
+          <t>48CD504B8C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -945,11 +971,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -959,17 +987,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -991,21 +1019,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>282A67BF24</t>
+          <t>D6018A3B1C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1014,11 +1044,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -1028,17 +1060,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1060,21 +1092,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16839F8C12</t>
+          <t>DE1E970986</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1083,11 +1117,13 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H10" t="n">
         <v>9</v>
@@ -1097,17 +1133,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1129,21 +1165,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F49297C25D</t>
+          <t>E819A8D449</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1152,11 +1190,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -1166,17 +1206,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1198,21 +1238,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F02DDD04D6</t>
+          <t>0708A93931</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1221,11 +1263,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H12" t="n">
         <v>11</v>
@@ -1235,17 +1279,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1267,21 +1311,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>75DA835969</t>
+          <t>81C8BB0695</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UIB-25-00024</t>
+          <t>POL-25-00030</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1023013161</v>
+          <t>ANDRES CORTES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1290,11 +1336,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1231231231231321</v>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3456098</t>
+        </is>
       </c>
       <c r="H13" t="n">
         <v>12</v>
@@ -1304,17 +1352,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1328,882 +1376,6 @@
         </is>
       </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>351C8CF081</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>9E19E5C6FB</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>9CFCB59F0A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>FDC9D07823</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>D011BBEDA9</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>C0D44CEFAB</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>12</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>965C561620</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A048EA1BD8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EB8394370A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I22" t="n">
-        <v>12</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20EB8B749A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CC62859AD2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>11</v>
-      </c>
-      <c r="I24" t="n">
-        <v>12</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>05FC5084E5</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>UIB-25-00025</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Camilo Cortes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1023013161</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ALLIANZ SEGUROS S.A.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>AU - AUTOMOVILES</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1231231231231321</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>12</v>
-      </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Cobro</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
